--- a/artfynd/A 43899-2025 artfynd.xlsx
+++ b/artfynd/A 43899-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>100818816</v>
       </c>
       <c r="B2" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485681.7347880983</v>
+        <v>485682</v>
       </c>
       <c r="R2" t="n">
-        <v>6316832.371920184</v>
+        <v>6316832</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,19 +755,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
